--- a/artfynd/A 20744-2026 artfynd.xlsx
+++ b/artfynd/A 20744-2026 artfynd.xlsx
@@ -813,7 +813,7 @@
         <v>133479465</v>
       </c>
       <c r="B3" t="n">
-        <v>57955</v>
+        <v>57962</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>133478830</v>
       </c>
       <c r="B4" t="n">
-        <v>57955</v>
+        <v>57962</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         <v>133480192</v>
       </c>
       <c r="B5" t="n">
-        <v>57955</v>
+        <v>57962</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>133478580</v>
       </c>
       <c r="B6" t="n">
-        <v>57955</v>
+        <v>57962</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>133478387</v>
       </c>
       <c r="B7" t="n">
-        <v>58641</v>
+        <v>58648</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 20744-2026 artfynd.xlsx
+++ b/artfynd/A 20744-2026 artfynd.xlsx
@@ -813,7 +813,7 @@
         <v>133479465</v>
       </c>
       <c r="B3" t="n">
-        <v>57962</v>
+        <v>57972</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>133478830</v>
       </c>
       <c r="B4" t="n">
-        <v>57962</v>
+        <v>57972</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         <v>133480192</v>
       </c>
       <c r="B5" t="n">
-        <v>57962</v>
+        <v>57972</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>133478580</v>
       </c>
       <c r="B6" t="n">
-        <v>57962</v>
+        <v>57972</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>133478387</v>
       </c>
       <c r="B7" t="n">
-        <v>58648</v>
+        <v>58658</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 20744-2026 artfynd.xlsx
+++ b/artfynd/A 20744-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>56822188</v>
+        <v>133478580</v>
       </c>
       <c r="B2" t="n">
-        <v>42705</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57972</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100943</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Asknätfjäril</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Euphydryas maturna</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,34 +703,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>kolonier</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
+      <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Spångabäcken naturreservat yta 13, Vstm</t>
+          <t>Spännartorpet, Spännartorpet, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>507635.7546219485</v>
+        <v>507679</v>
       </c>
       <c r="R2" t="n">
-        <v>6606826.307522229</v>
+        <v>6606941</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,27 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2015-07-25</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2015-09-09</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Räkning av larvkolonier inom Biogeografisk uppföljning av fjärilar.</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,30 +775,26 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Henrik Josefsson</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Claes Urban Eliasson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Biogeografisk uppföljning av fjärilar</t>
-        </is>
-      </c>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133479465</v>
+        <v>133478830</v>
       </c>
       <c r="B3" t="n">
         <v>57972</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -850,13 +827,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>507705</v>
+        <v>507702</v>
       </c>
       <c r="R3" t="n">
-        <v>6606928</v>
+        <v>6606999</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -885,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -895,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -922,14 +899,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133478830</v>
+        <v>133479465</v>
       </c>
       <c r="B4" t="n">
         <v>57972</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -962,13 +939,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>507702</v>
+        <v>507705</v>
       </c>
       <c r="R4" t="n">
-        <v>6606999</v>
+        <v>6606928</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -997,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1007,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1041,7 +1018,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1146,27 +1123,27 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133478580</v>
+        <v>56822188</v>
       </c>
       <c r="B6" t="n">
-        <v>57972</v>
+        <v>43428</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>100943</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Asknätfjäril</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Euphydryas maturna</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1174,25 +1151,34 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Spännartorpet, Spännartorpet, Vstm</t>
+          <t>Spångabäcken naturreservat yta 13, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>507679</v>
+        <v>507636</v>
       </c>
       <c r="R6" t="n">
-        <v>6606941</v>
+        <v>6606826</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1216,22 +1202,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>14:48</t>
+          <t>2015-07-25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>14:48</t>
+          <t>2015-09-09</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Räkning av larvkolonier inom Biogeografisk uppföljning av fjärilar.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1246,15 +1227,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Henrik Josefsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Claes Urban Eliasson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1367,6 +1352,116 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>54806505</v>
+      </c>
+      <c r="B8" t="n">
+        <v>43258</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>201129</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vitfläckig guldvinge</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lycaena virgaureae</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Spännartorpet, Vstm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>507635</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6606800</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2015-08-10</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2015-08-10</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Claes Urban Eliasson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Claes Urban Eliasson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 20744-2026 artfynd.xlsx
+++ b/artfynd/A 20744-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133478580</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133478830</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1008,6 +1023,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133479465</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1120,6 +1140,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133480192</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1240,6 +1265,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56822188</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1352,6 +1382,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133478387</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1462,8 +1497,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54806505</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>